--- a/uploads/class_type.xlsx
+++ b/uploads/class_type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6B5DBA-5D69-4AEE-AFA6-F2DDD4CE2480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBA8B22-4E5C-4BFE-853B-0EC94E821669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -406,9 +406,6 @@
     <t>IT W/S/PHY LAB</t>
   </si>
   <si>
-    <t>CP/IT W/S</t>
-  </si>
-  <si>
     <t>PROJ</t>
   </si>
   <si>
@@ -446,6 +443,9 @@
   </si>
   <si>
     <t>OS LAB/DBMS LAB</t>
+  </si>
+  <si>
+    <t>CP LAB/IT W/S</t>
   </si>
 </sst>
 </file>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B121" t="s">
         <v>12</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B127" t="s">
         <v>12</v>
@@ -1880,7 +1880,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B131" t="s">
         <v>12</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B133" t="s">
         <v>12</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B134" t="s">
         <v>11</v>
@@ -1912,7 +1912,7 @@
     </row>
     <row r="135" spans="1:2" ht="18" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B135" t="s">
         <v>12</v>
@@ -1920,7 +1920,7 @@
     </row>
     <row r="136" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B136" t="s">
         <v>12</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B137" t="s">
         <v>12</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B138" t="s">
         <v>12</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B139" t="s">
         <v>12</v>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B140" t="s">
         <v>12</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141" t="s">
         <v>12</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B142" t="s">
         <v>12</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B143" t="s">
         <v>12</v>
